--- a/db_tables/events.xlsx
+++ b/db_tables/events.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\airno\Desktop\Files\code\IronDoom\src\db\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\airno\Desktop\Files\code\IronDoom\db_tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31831D5A-2BF3-4232-B36E-C3F86FF0B08D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD9D48CD-ADCE-44A8-9B2B-A322C36043F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="16">
   <si>
     <t>נשיא אמריקאי אוהב ישראל עלה לשלטון!</t>
   </si>
@@ -39,7 +39,40 @@
     <t>BAD</t>
   </si>
   <si>
-    <t>יוני, בנו הקטן של יהוחפץ שלזינגר ממושב נחם, חפר בגינה כדי לקבור את אוגר המחמד שלו, ובטעות מצא באר נפט. כתוצאה מכך, אבא שלזינגר התעשר ושילם ושילם חמישים אחוז מס על הרווחים.</t>
+    <t>יוני, בנו הקטן של יהוחפץ שלזינגר ממושב נחם, חפר בגינה כדי לקבור את אוגר המחמד שלו שנפטר בדמי ימיו - ובטעות מצא באר נפט. כתוצאה מכך, אבא שלזינגר התעשר ושילם ונאלץ לשלם חמישים אחוז מס על הרווחים.</t>
+  </si>
+  <si>
+    <t>טירון של יוניפיל בשם ז'אן-ז'אק מצא בסבך הלבנוני פטריה מעניינת, ואמר לעצמו: "Omelette aux champignons!". לאחר שביצע את זממו הקולינרי, מיודענו ז'אן ז'אק חש סחרחר במהלך ששמר בחמ"ל, ונרדם על כל הכפתורים...</t>
+  </si>
+  <si>
+    <t>בבור שבקריה הוחלט שאין סיבה שצה"ל לא יעשה גם הוא יום 'הבא את בתך לעבודה'. ואם נצטט את אל"מ ג' (שביקש לא לצטט אותו): "מה כבר יכול להשתבש?"</t>
+  </si>
+  <si>
+    <t>בפסיקת בג"ץ 165/5 "מירה נגד מיר" הכריעו השופטים המכובדים שעל הישיבות החרדיות לשלב נשים. הציבור החרדי עמד על הרגליים האחוריות עם הסיסמה: 'נתגייס ולא נלמד', ובחורי הישיבות הק' צבאו על לשכות הגיוס.</t>
+  </si>
+  <si>
+    <t>האיראנים הצליחו לשים את ידם על משלוחי הקפה הטורקי הצבאיים המיועדים לחיל הטנ"א, במטרה לגרום לטכנאי צה"ל לסבול מהרעלת קפאין. אלא שחלה טעות במינון, ובמקום לגרום לגרום להרעלה, הם גרמו לטכנאי צה"ל העייפים להיות היפר-אקטיביים.</t>
+  </si>
+  <si>
+    <t>תיאור</t>
+  </si>
+  <si>
+    <t>סיווג</t>
+  </si>
+  <si>
+    <t>חוצנים חטפו את כל הדרג הפקידותי, והחליפו אותו בפומלות ובאשכוליות. בהתחלה שררה פאניקה ברחבי המדינה, אבל די מהר התברר שהפומלות דווקא עובדות באופן יעיל למדי, והסערה שככה. האשכוליות אגב, פוטרו לאלתר וכעת מחפשות עבודה בלשכת האבטלה.</t>
+  </si>
+  <si>
+    <t>פרפר השיק את כנפיו בסין.</t>
+  </si>
+  <si>
+    <t>האחמ"ש חיפש את המפתחות למחסן, לצורך מבצעי דחוף, אבל המפתחות לא נמצאים. איפה המפתחות? גליק, שאלתי אותך איפה המפתחות! אצל הג'ינג'י עונה גליק, והיום הג'ינג'י לא נמצא...</t>
+  </si>
+  <si>
+    <t>צבי-פנחס אהרונוף, תותח שמדכא ונכה צה"ל, זכה בתחרות האוריגמי הבינלאומית, ואיתה גם בדעת הקהל הבינלאומי - שהזיל דמעה או שתיים על סיפורו קורע הלב.</t>
+  </si>
+  <si>
+    <t>על הדמ"צ שעמלו עליו במשך חודשים נשפך קפה, וחלק מהשורות טושטשו. נו שוין, אמר לעצמו ס', קפט ותיק, מה יש? אף אחד לא מת מקצת קפה.</t>
   </si>
 </sst>
 </file>
@@ -75,8 +108,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -357,31 +393,123 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="34.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="4" spans="1:2" ht="70" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>1</v>
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="84" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="56" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="70" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="84" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="84" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="70" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="56" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="56" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
